--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/97.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/97.xlsx
@@ -426,13 +426,13 @@
         <v>-16.55421534690226</v>
       </c>
       <c r="E2">
-        <v>-6.994633215741151</v>
+        <v>-8.223941826811362</v>
       </c>
       <c r="F2">
-        <v>-3.712250796357629</v>
+        <v>-4.245933122550433</v>
       </c>
       <c r="G2">
-        <v>-7.85761078303835</v>
+        <v>-8.515998837706446</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-16.29646922889751</v>
       </c>
       <c r="E3">
-        <v>-8.320063216098173</v>
+        <v>-9.104571524712979</v>
       </c>
       <c r="F3">
-        <v>-3.791769925189368</v>
+        <v>-4.288031582328107</v>
       </c>
       <c r="G3">
-        <v>-7.229113644044332</v>
+        <v>-8.068724272077674</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-16.11367843992961</v>
       </c>
       <c r="E4">
-        <v>-9.414858035244544</v>
+        <v>-10.40719160149336</v>
       </c>
       <c r="F4">
-        <v>-3.723105722803914</v>
+        <v>-4.169957749467871</v>
       </c>
       <c r="G4">
-        <v>-7.203248351746007</v>
+        <v>-7.568500841093797</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-16.04228436929115</v>
       </c>
       <c r="E5">
-        <v>-8.905911898470487</v>
+        <v>-10.13909688329126</v>
       </c>
       <c r="F5">
-        <v>-3.569781543484948</v>
+        <v>-4.089756045896225</v>
       </c>
       <c r="G5">
-        <v>-8.052323829476125</v>
+        <v>-8.025369367695378</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-16.06226244780133</v>
       </c>
       <c r="E6">
-        <v>-9.280045364036196</v>
+        <v>-10.46693123060255</v>
       </c>
       <c r="F6">
-        <v>-3.347223245007402</v>
+        <v>-4.310404129142916</v>
       </c>
       <c r="G6">
-        <v>-7.347035276153172</v>
+        <v>-8.041895611027419</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-16.17207213046054</v>
       </c>
       <c r="E7">
-        <v>-11.13607666387195</v>
+        <v>-12.54047419397473</v>
       </c>
       <c r="F7">
-        <v>-3.494693351890783</v>
+        <v>-3.777369586259101</v>
       </c>
       <c r="G7">
-        <v>-7.155324894519517</v>
+        <v>-8.355341373231155</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-16.34625430107257</v>
       </c>
       <c r="E8">
-        <v>-12.27866952616928</v>
+        <v>-12.18526522128708</v>
       </c>
       <c r="F8">
-        <v>-2.987102113783956</v>
+        <v>-3.724383893706433</v>
       </c>
       <c r="G8">
-        <v>-7.609700580330027</v>
+        <v>-8.363339651254034</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-16.57088278307609</v>
       </c>
       <c r="E9">
-        <v>-12.43747405267027</v>
+        <v>-12.64097914610097</v>
       </c>
       <c r="F9">
-        <v>-3.548077489164198</v>
+        <v>-3.747629539763793</v>
       </c>
       <c r="G9">
-        <v>-7.641521544053502</v>
+        <v>-8.055253662278378</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-16.81654337821434</v>
       </c>
       <c r="E10">
-        <v>-13.32973740029759</v>
+        <v>-13.46067822622938</v>
       </c>
       <c r="F10">
-        <v>-3.02826286166166</v>
+        <v>-3.606149357570054</v>
       </c>
       <c r="G10">
-        <v>-7.199560404015259</v>
+        <v>-8.639475565230184</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-17.0636336593131</v>
       </c>
       <c r="E11">
-        <v>-13.73561999713108</v>
+        <v>-14.56482434420159</v>
       </c>
       <c r="F11">
-        <v>-2.686572076783101</v>
+        <v>-3.096811092610722</v>
       </c>
       <c r="G11">
-        <v>-7.257240038945981</v>
+        <v>-7.984676141926657</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-17.28651086165687</v>
       </c>
       <c r="E12">
-        <v>-14.96217529600462</v>
+        <v>-15.21618646004287</v>
       </c>
       <c r="F12">
-        <v>-2.704945265777194</v>
+        <v>-3.309810859627365</v>
       </c>
       <c r="G12">
-        <v>-7.159234648801396</v>
+        <v>-7.842590837926676</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-17.46888452484095</v>
       </c>
       <c r="E13">
-        <v>-16.02942340776234</v>
+        <v>-16.20889136116032</v>
       </c>
       <c r="F13">
-        <v>-2.298830691248111</v>
+        <v>-2.756080385552007</v>
       </c>
       <c r="G13">
-        <v>-6.731214216029024</v>
+        <v>-8.213941352157804</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-17.60140610410693</v>
       </c>
       <c r="E14">
-        <v>-17.40136536465214</v>
+        <v>-15.9305713486489</v>
       </c>
       <c r="F14">
-        <v>-2.150941430458913</v>
+        <v>-2.628787651866016</v>
       </c>
       <c r="G14">
-        <v>-7.565236643192075</v>
+        <v>-7.497158584722503</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-17.68256618817304</v>
       </c>
       <c r="E15">
-        <v>-17.48890982416842</v>
+        <v>-17.52719807190327</v>
       </c>
       <c r="F15">
-        <v>-1.636852478444525</v>
+        <v>-2.357019359457762</v>
       </c>
       <c r="G15">
-        <v>-6.629709579249431</v>
+        <v>-7.370728850577736</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-17.72175865451084</v>
       </c>
       <c r="E16">
-        <v>-18.24384266903913</v>
+        <v>-19.05673998120802</v>
       </c>
       <c r="F16">
-        <v>-1.412629161487352</v>
+        <v>-1.9931059622643</v>
       </c>
       <c r="G16">
-        <v>-6.990823886673132</v>
+        <v>-7.024829810452526</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-17.72690827697306</v>
       </c>
       <c r="E17">
-        <v>-18.26526235109541</v>
+        <v>-19.44976171185973</v>
       </c>
       <c r="F17">
-        <v>-1.182224566970489</v>
+        <v>-1.837526966874914</v>
       </c>
       <c r="G17">
-        <v>-6.473471693069066</v>
+        <v>-7.526950184030405</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-17.71394276723311</v>
       </c>
       <c r="E18">
-        <v>-19.76303701523635</v>
+        <v>-20.81852920847015</v>
       </c>
       <c r="F18">
-        <v>-0.4675605306140495</v>
+        <v>-1.296598911009823</v>
       </c>
       <c r="G18">
-        <v>-6.113522697675189</v>
+        <v>-7.328271104036584</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-17.68464765087936</v>
       </c>
       <c r="E19">
-        <v>-20.94870472229465</v>
+        <v>-21.06391362952379</v>
       </c>
       <c r="F19">
-        <v>-0.3087127974532163</v>
+        <v>-1.084087880760832</v>
       </c>
       <c r="G19">
-        <v>-6.769997257021587</v>
+        <v>-6.849056395044922</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-17.64861515926217</v>
       </c>
       <c r="E20">
-        <v>-22.78695723317629</v>
+        <v>-21.8039704372793</v>
       </c>
       <c r="F20">
-        <v>0.1559135085726096</v>
+        <v>-0.5229261227149601</v>
       </c>
       <c r="G20">
-        <v>-6.771046699957536</v>
+        <v>-6.818923809546476</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-17.59688826057389</v>
       </c>
       <c r="E21">
-        <v>-23.16487650301241</v>
+        <v>-22.27873565224346</v>
       </c>
       <c r="F21">
-        <v>0.336211815628936</v>
+        <v>0.01843185583218405</v>
       </c>
       <c r="G21">
-        <v>-6.204655395280246</v>
+        <v>-6.739781907884659</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-17.53252119091692</v>
       </c>
       <c r="E22">
-        <v>-23.60266672770394</v>
+        <v>-23.01968456937848</v>
       </c>
       <c r="F22">
-        <v>0.9784483764890038</v>
+        <v>-0.09062436948117647</v>
       </c>
       <c r="G22">
-        <v>-6.127248219481007</v>
+        <v>-7.366719779929679</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-17.44227850412515</v>
       </c>
       <c r="E23">
-        <v>-23.79576085939101</v>
+        <v>-23.31025410408065</v>
       </c>
       <c r="F23">
-        <v>1.048367555489699</v>
+        <v>0.2363976854286096</v>
       </c>
       <c r="G23">
-        <v>-5.923139844802781</v>
+        <v>-6.530638193441201</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-17.32632494629977</v>
       </c>
       <c r="E24">
-        <v>-24.49124389748902</v>
+        <v>-24.30928075491281</v>
       </c>
       <c r="F24">
-        <v>0.8686979792920974</v>
+        <v>0.4386767215182208</v>
       </c>
       <c r="G24">
-        <v>-6.480311280153201</v>
+        <v>-7.584119994948079</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-17.17282843676906</v>
       </c>
       <c r="E25">
-        <v>-24.9955981616193</v>
+        <v>-25.14223920693568</v>
       </c>
       <c r="F25">
-        <v>1.198321936214077</v>
+        <v>0.5751245717399526</v>
       </c>
       <c r="G25">
-        <v>-6.251598931027112</v>
+        <v>-7.136474648218907</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-16.98693315895162</v>
       </c>
       <c r="E26">
-        <v>-24.48223223421376</v>
+        <v>-24.33195935274322</v>
       </c>
       <c r="F26">
-        <v>1.270650007622113</v>
+        <v>0.7101840781945924</v>
       </c>
       <c r="G26">
-        <v>-6.042226788941445</v>
+        <v>-7.263152673279119</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-16.764410626289</v>
       </c>
       <c r="E27">
-        <v>-25.05021608662581</v>
+        <v>-24.69770155597272</v>
       </c>
       <c r="F27">
-        <v>1.46383191289418</v>
+        <v>0.8186215130580616</v>
       </c>
       <c r="G27">
-        <v>-6.539675982763412</v>
+        <v>-6.694920705281994</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-16.51210450242235</v>
       </c>
       <c r="E28">
-        <v>-24.78373803364445</v>
+        <v>-23.81846662806547</v>
       </c>
       <c r="F28">
-        <v>1.1343852265964</v>
+        <v>0.6962343711314487</v>
       </c>
       <c r="G28">
-        <v>-6.907785472911593</v>
+        <v>-6.992595028536642</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-16.23049090076587</v>
       </c>
       <c r="E29">
-        <v>-24.72144434519494</v>
+        <v>-24.38357942795666</v>
       </c>
       <c r="F29">
-        <v>1.117524636479819</v>
+        <v>0.6361967868787489</v>
       </c>
       <c r="G29">
-        <v>-5.993611427697247</v>
+        <v>-7.26074259612653</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-15.92604732345249</v>
       </c>
       <c r="E30">
-        <v>-24.67414896265883</v>
+        <v>-24.31496851826644</v>
       </c>
       <c r="F30">
-        <v>1.333741782488934</v>
+        <v>0.3398881101625602</v>
       </c>
       <c r="G30">
-        <v>-6.355000510400708</v>
+        <v>-6.468449595485992</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-15.60479246156933</v>
       </c>
       <c r="E31">
-        <v>-24.14995092542694</v>
+        <v>-24.0074670192496</v>
       </c>
       <c r="F31">
-        <v>1.216547675810471</v>
+        <v>0.8984628768094892</v>
       </c>
       <c r="G31">
-        <v>-6.40132166358619</v>
+        <v>-6.675782441519468</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-15.27176255275221</v>
       </c>
       <c r="E32">
-        <v>-23.79777150185041</v>
+        <v>-22.69514695114478</v>
       </c>
       <c r="F32">
-        <v>0.8356676574728699</v>
+        <v>0.6067615795876713</v>
       </c>
       <c r="G32">
-        <v>-6.217821434889927</v>
+        <v>-7.160247675736414</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-14.93634091778129</v>
       </c>
       <c r="E33">
-        <v>-23.48872126472294</v>
+        <v>-22.7268598546205</v>
       </c>
       <c r="F33">
-        <v>0.859035901905844</v>
+        <v>0.3407313881786101</v>
       </c>
       <c r="G33">
-        <v>-5.886406031499028</v>
+        <v>-7.110195537728172</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-14.59999787013174</v>
       </c>
       <c r="E34">
-        <v>-23.08232695032659</v>
+        <v>-23.03054837852288</v>
       </c>
       <c r="F34">
-        <v>0.7910517891580885</v>
+        <v>0.1978653473199878</v>
       </c>
       <c r="G34">
-        <v>-5.977396375645897</v>
+        <v>-6.708239029986482</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-14.27378212700165</v>
       </c>
       <c r="E35">
-        <v>-22.14381429765893</v>
+        <v>-22.02793970475066</v>
       </c>
       <c r="F35">
-        <v>0.8488287587685485</v>
+        <v>0.1777940051501557</v>
       </c>
       <c r="G35">
-        <v>-5.031494061983176</v>
+        <v>-6.433318086223246</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-13.95553794088464</v>
       </c>
       <c r="E36">
-        <v>-22.06812538309473</v>
+        <v>-22.43079275247301</v>
       </c>
       <c r="F36">
-        <v>0.4287785594221695</v>
+        <v>0.0438138614213637</v>
       </c>
       <c r="G36">
-        <v>-5.134339469706175</v>
+        <v>-6.415414655946868</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-13.65498303619889</v>
       </c>
       <c r="E37">
-        <v>-20.90291279312908</v>
+        <v>-21.99790233665778</v>
       </c>
       <c r="F37">
-        <v>0.443419124899248</v>
+        <v>0.06080947542460115</v>
       </c>
       <c r="G37">
-        <v>-4.387824692782679</v>
+        <v>-6.796438584243746</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-13.36612509842889</v>
       </c>
       <c r="E38">
-        <v>-21.46464282293654</v>
+        <v>-21.26693417623567</v>
       </c>
       <c r="F38">
-        <v>0.389158574913672</v>
+        <v>-0.1353214178014322</v>
       </c>
       <c r="G38">
-        <v>-5.385523801952837</v>
+        <v>-6.400427816290587</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-13.09631353753122</v>
       </c>
       <c r="E39">
-        <v>-20.95947796195889</v>
+        <v>-20.2520216385846</v>
       </c>
       <c r="F39">
-        <v>0.1530581261351597</v>
+        <v>-0.02309917227457197</v>
       </c>
       <c r="G39">
-        <v>-3.801460866866967</v>
+        <v>-5.56420718688946</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-12.83688781733483</v>
       </c>
       <c r="E40">
-        <v>-19.53319431697705</v>
+        <v>-19.15007635898012</v>
       </c>
       <c r="F40">
-        <v>0.3521148130278809</v>
+        <v>-0.1561929628823685</v>
       </c>
       <c r="G40">
-        <v>-4.865023279540925</v>
+        <v>-5.859451569718282</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-12.59199371854275</v>
       </c>
       <c r="E41">
-        <v>-19.56872925251523</v>
+        <v>-19.97171362598381</v>
       </c>
       <c r="F41">
-        <v>0.1533157483974303</v>
+        <v>-0.4034854836401049</v>
       </c>
       <c r="G41">
-        <v>-4.547270497590597</v>
+        <v>-5.684446200875789</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-12.35132106312079</v>
       </c>
       <c r="E42">
-        <v>-18.46354611399527</v>
+        <v>-19.75569183039591</v>
       </c>
       <c r="F42">
-        <v>-0.3370305371179174</v>
+        <v>-0.6552892932734875</v>
       </c>
       <c r="G42">
-        <v>-4.11496290834487</v>
+        <v>-5.942082786378491</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-12.11496660220343</v>
       </c>
       <c r="E43">
-        <v>-18.54512204476944</v>
+        <v>-19.20832612014078</v>
       </c>
       <c r="F43">
-        <v>0.08902698263356351</v>
+        <v>-0.4827850951101016</v>
       </c>
       <c r="G43">
-        <v>-4.289713365180838</v>
+        <v>-5.485959132523246</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-11.871631379708</v>
       </c>
       <c r="E44">
-        <v>-18.26805641955815</v>
+        <v>-17.97745065706392</v>
       </c>
       <c r="F44">
-        <v>-0.4730352107791514</v>
+        <v>-0.8109237892788613</v>
       </c>
       <c r="G44">
-        <v>-4.075292641147783</v>
+        <v>-5.454988979003365</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-11.62045949697563</v>
       </c>
       <c r="E45">
-        <v>-16.89114219820792</v>
+        <v>-17.89156814750845</v>
       </c>
       <c r="F45">
-        <v>-0.4209690060435913</v>
+        <v>-0.6156900179500598</v>
       </c>
       <c r="G45">
-        <v>-4.118313180430612</v>
+        <v>-4.575582283042444</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-11.3522557395032</v>
       </c>
       <c r="E46">
-        <v>-17.57135522195207</v>
+        <v>-16.20265565245176</v>
       </c>
       <c r="F46">
-        <v>-0.4353726584434691</v>
+        <v>-0.8452413940420394</v>
       </c>
       <c r="G46">
-        <v>-4.191979439770474</v>
+        <v>-5.025607912014352</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-11.06617671696477</v>
       </c>
       <c r="E47">
-        <v>-16.01049438641027</v>
+        <v>-16.38407990662105</v>
       </c>
       <c r="F47">
-        <v>-0.6001879503740699</v>
+        <v>-0.9053767256482694</v>
       </c>
       <c r="G47">
-        <v>-3.926854400257942</v>
+        <v>-4.738610098123854</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-10.75815669052594</v>
       </c>
       <c r="E48">
-        <v>-15.61847344851427</v>
+        <v>-15.54033915798592</v>
       </c>
       <c r="F48">
-        <v>-0.7133470794334964</v>
+        <v>-1.070180420435231</v>
       </c>
       <c r="G48">
-        <v>-3.576270938194662</v>
+        <v>-5.439323477511533</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-10.42783264948614</v>
       </c>
       <c r="E49">
-        <v>-14.93337420131584</v>
+        <v>-15.60152337030356</v>
       </c>
       <c r="F49">
-        <v>-0.7842876354418433</v>
+        <v>-1.201138679878611</v>
       </c>
       <c r="G49">
-        <v>-4.129691525449087</v>
+        <v>-4.912393875662356</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-10.07623179470848</v>
       </c>
       <c r="E50">
-        <v>-14.80387343011849</v>
+        <v>-15.32312184526</v>
       </c>
       <c r="F50">
-        <v>-0.9438784141629877</v>
+        <v>-1.463275544494514</v>
       </c>
       <c r="G50">
-        <v>-3.983110500606777</v>
+        <v>-4.554626529778858</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-9.70424558773926</v>
       </c>
       <c r="E51">
-        <v>-15.35893301771265</v>
+        <v>-14.37845499641591</v>
       </c>
       <c r="F51">
-        <v>-0.9554266841254155</v>
+        <v>-1.723293445294056</v>
       </c>
       <c r="G51">
-        <v>-3.735624047727481</v>
+        <v>-5.036165241739088</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-9.319246062879364</v>
       </c>
       <c r="E52">
-        <v>-14.14354493574202</v>
+        <v>-14.39593037761152</v>
       </c>
       <c r="F52">
-        <v>-1.065140633156599</v>
+        <v>-1.49649473408158</v>
       </c>
       <c r="G52">
-        <v>-4.386887808395065</v>
+        <v>-5.041303208416037</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-8.923188601161781</v>
       </c>
       <c r="E53">
-        <v>-13.60872762696215</v>
+        <v>-14.57213782972398</v>
       </c>
       <c r="F53">
-        <v>-1.238405272595755</v>
+        <v>-1.71484078431589</v>
       </c>
       <c r="G53">
-        <v>-4.490478088864401</v>
+        <v>-4.948270257671438</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-8.527985016795775</v>
       </c>
       <c r="E54">
-        <v>-12.70608048843524</v>
+        <v>-13.2924318314224</v>
       </c>
       <c r="F54">
-        <v>-1.257667299813052</v>
+        <v>-1.542014351232815</v>
       </c>
       <c r="G54">
-        <v>-4.529204850582794</v>
+        <v>-4.697834108716651</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-8.133522975487951</v>
       </c>
       <c r="E55">
-        <v>-12.51239312665317</v>
+        <v>-13.13081965103666</v>
       </c>
       <c r="F55">
-        <v>-1.1079572874725</v>
+        <v>-1.434498060921259</v>
       </c>
       <c r="G55">
-        <v>-3.70006216754463</v>
+        <v>-4.833407569640885</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-7.751166893208646</v>
       </c>
       <c r="E56">
-        <v>-12.31272817918097</v>
+        <v>-13.22496662565613</v>
       </c>
       <c r="F56">
-        <v>-1.207955315236248</v>
+        <v>-1.539867222924759</v>
       </c>
       <c r="G56">
-        <v>-4.574724851747773</v>
+        <v>-4.663874532574807</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-7.379425293102377</v>
       </c>
       <c r="E57">
-        <v>-12.35131530620033</v>
+        <v>-12.78393401357511</v>
       </c>
       <c r="F57">
-        <v>-1.228637992549346</v>
+        <v>-2.008955944149466</v>
       </c>
       <c r="G57">
-        <v>-4.422780743131844</v>
+        <v>-5.24633522529972</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-7.028044244736003</v>
       </c>
       <c r="E58">
-        <v>-10.84907556668783</v>
+        <v>-12.36763592652398</v>
       </c>
       <c r="F58">
-        <v>-1.203497041874381</v>
+        <v>-1.862701880613394</v>
       </c>
       <c r="G58">
-        <v>-4.471770196021978</v>
+        <v>-5.260603676573978</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-6.695775035734181</v>
       </c>
       <c r="E59">
-        <v>-11.64349217643142</v>
+        <v>-11.9551462861133</v>
       </c>
       <c r="F59">
-        <v>-1.156900547099506</v>
+        <v>-1.850144659154356</v>
       </c>
       <c r="G59">
-        <v>-5.172268389949605</v>
+        <v>-5.760827107557854</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-6.390013476049326</v>
       </c>
       <c r="E60">
-        <v>-9.779694543672505</v>
+        <v>-11.03069907371347</v>
       </c>
       <c r="F60">
-        <v>-1.209502705544677</v>
+        <v>-1.541502420177885</v>
       </c>
       <c r="G60">
-        <v>-4.275193312445595</v>
+        <v>-5.06549998576257</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-6.108820228457678</v>
       </c>
       <c r="E61">
-        <v>-11.27522761317965</v>
+        <v>-11.33811000325016</v>
       </c>
       <c r="F61">
-        <v>-1.469860236979367</v>
+        <v>-1.744078840165102</v>
       </c>
       <c r="G61">
-        <v>-5.321060859212149</v>
+        <v>-5.560006104600125</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-5.857884113332353</v>
       </c>
       <c r="E62">
-        <v>-9.43045409972696</v>
+        <v>-10.76205188168243</v>
       </c>
       <c r="F62">
-        <v>-1.291769529051502</v>
+        <v>-1.894174043347955</v>
       </c>
       <c r="G62">
-        <v>-5.036910114485424</v>
+        <v>-5.334845970837674</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-5.633589230629952</v>
       </c>
       <c r="E63">
-        <v>-9.871731249404398</v>
+        <v>-11.1096530180372</v>
       </c>
       <c r="F63">
-        <v>-1.83476518995398</v>
+        <v>-2.433438737468225</v>
       </c>
       <c r="G63">
-        <v>-5.56843475354311</v>
+        <v>-5.737252712772705</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-5.438686819117154</v>
       </c>
       <c r="E64">
-        <v>-9.749666232527645</v>
+        <v>-10.80120959642676</v>
       </c>
       <c r="F64">
-        <v>-1.664194401308728</v>
+        <v>-1.992436641402838</v>
       </c>
       <c r="G64">
-        <v>-5.140437494589513</v>
+        <v>-6.105037769458037</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-5.269859069483031</v>
       </c>
       <c r="E65">
-        <v>-8.883192544374005</v>
+        <v>-10.79778154160295</v>
       </c>
       <c r="F65">
-        <v>-1.370620993756584</v>
+        <v>-1.960080610649489</v>
       </c>
       <c r="G65">
-        <v>-5.555871233221575</v>
+        <v>-6.466228219429141</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-5.128910877359304</v>
       </c>
       <c r="E66">
-        <v>-9.261075586418066</v>
+        <v>-10.71228395233813</v>
       </c>
       <c r="F66">
-        <v>-1.789859393048219</v>
+        <v>-2.350663296376082</v>
       </c>
       <c r="G66">
-        <v>-5.624783549167044</v>
+        <v>-6.547190921137557</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-5.013139694073956</v>
       </c>
       <c r="E67">
-        <v>-10.09671489505348</v>
+        <v>-10.31308085466596</v>
       </c>
       <c r="F67">
-        <v>-1.96779768137397</v>
+        <v>-2.429870959064368</v>
       </c>
       <c r="G67">
-        <v>-5.60877044039359</v>
+        <v>-6.438095203436415</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-4.922041166262714</v>
       </c>
       <c r="E68">
-        <v>-9.474176516271017</v>
+        <v>-10.07390949995085</v>
       </c>
       <c r="F68">
-        <v>-2.302124280041642</v>
+        <v>-2.074221355081233</v>
       </c>
       <c r="G68">
-        <v>-6.067314103038042</v>
+        <v>-7.088690233905067</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-4.851932946174034</v>
       </c>
       <c r="E69">
-        <v>-8.622995484841281</v>
+        <v>-10.01668317391592</v>
       </c>
       <c r="F69">
-        <v>-2.145510653766159</v>
+        <v>-2.356257261447187</v>
       </c>
       <c r="G69">
-        <v>-6.053578649595606</v>
+        <v>-6.50098232650041</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-4.799025783997215</v>
       </c>
       <c r="E70">
-        <v>-9.200801597375973</v>
+        <v>-10.55815281101306</v>
       </c>
       <c r="F70">
-        <v>-1.84792960471927</v>
+        <v>-2.421910348323464</v>
       </c>
       <c r="G70">
-        <v>-5.764051578913104</v>
+        <v>-6.147952371283609</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-4.758773521993409</v>
       </c>
       <c r="E71">
-        <v>-8.777113040744327</v>
+        <v>-10.37758443843122</v>
       </c>
       <c r="F71">
-        <v>-2.097278961738158</v>
+        <v>-2.482346377296911</v>
       </c>
       <c r="G71">
-        <v>-5.79623008155482</v>
+        <v>-6.705630320101537</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-4.7251134203247</v>
       </c>
       <c r="E72">
-        <v>-9.033945444089351</v>
+        <v>-9.622230445477792</v>
       </c>
       <c r="F72">
-        <v>-2.188577475037705</v>
+        <v>-2.522460897144879</v>
       </c>
       <c r="G72">
-        <v>-5.854081864853584</v>
+        <v>-6.040233840526803</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-4.693583798887771</v>
       </c>
       <c r="E73">
-        <v>-9.105572317468674</v>
+        <v>-10.26178230110707</v>
       </c>
       <c r="F73">
-        <v>-2.26878497718117</v>
+        <v>-2.641069855347324</v>
       </c>
       <c r="G73">
-        <v>-5.777181202521854</v>
+        <v>-4.991721167874372</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-4.657479319652554</v>
       </c>
       <c r="E74">
-        <v>-9.62886465989903</v>
+        <v>-10.75837023231419</v>
       </c>
       <c r="F74">
-        <v>-2.492086321219027</v>
+        <v>-2.832320007836063</v>
       </c>
       <c r="G74">
-        <v>-4.83356647582677</v>
+        <v>-5.692408062897737</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-4.613669069698071</v>
       </c>
       <c r="E75">
-        <v>-10.02141090077993</v>
+        <v>-10.37465904422226</v>
       </c>
       <c r="F75">
-        <v>-2.495394820625808</v>
+        <v>-2.766802773213844</v>
       </c>
       <c r="G75">
-        <v>-5.223777167995125</v>
+        <v>-5.359102338003914</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-4.556048639337294</v>
       </c>
       <c r="E76">
-        <v>-9.83875943015455</v>
+        <v>-10.50583535080245</v>
       </c>
       <c r="F76">
-        <v>-2.629939082555907</v>
+        <v>-2.905741524215794</v>
       </c>
       <c r="G76">
-        <v>-4.795452165033141</v>
+        <v>-4.973407229951124</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-4.483963852798468</v>
       </c>
       <c r="E77">
-        <v>-10.68506782355203</v>
+        <v>-12.07466630059774</v>
       </c>
       <c r="F77">
-        <v>-2.577414790646599</v>
+        <v>-3.105083997862481</v>
       </c>
       <c r="G77">
-        <v>-3.708447779395604</v>
+        <v>-4.652549156284961</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-4.394047637042685</v>
       </c>
       <c r="E78">
-        <v>-10.08387667124173</v>
+        <v>-11.57042977679166</v>
       </c>
       <c r="F78">
-        <v>-2.730603946078908</v>
+        <v>-3.254703718156128</v>
       </c>
       <c r="G78">
-        <v>-4.147743930274733</v>
+        <v>-4.631990668486086</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-4.290320632978403</v>
       </c>
       <c r="E79">
-        <v>-10.85738984496591</v>
+        <v>-11.8911453629629</v>
       </c>
       <c r="F79">
-        <v>-2.64455728211311</v>
+        <v>-3.143178957982425</v>
       </c>
       <c r="G79">
-        <v>-3.728128972626571</v>
+        <v>-5.042683705905913</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-4.173259050654246</v>
       </c>
       <c r="E80">
-        <v>-10.97450976822629</v>
+        <v>-12.626827664827</v>
       </c>
       <c r="F80">
-        <v>-2.921926994899093</v>
+        <v>-3.328918810507741</v>
       </c>
       <c r="G80">
-        <v>-3.845828798184279</v>
+        <v>-4.382603962467249</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-4.050125333398348</v>
       </c>
       <c r="E81">
-        <v>-12.43262405700805</v>
+        <v>-13.19444471084443</v>
       </c>
       <c r="F81">
-        <v>-2.79489105510797</v>
+        <v>-3.358479929644044</v>
       </c>
       <c r="G81">
-        <v>-2.972490332196844</v>
+        <v>-4.022946295080827</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-3.926536099530483</v>
       </c>
       <c r="E82">
-        <v>-13.37729543432614</v>
+        <v>-14.03737486263219</v>
       </c>
       <c r="F82">
-        <v>-2.852156922030902</v>
+        <v>-3.369577567739349</v>
       </c>
       <c r="G82">
-        <v>-2.852804179315573</v>
+        <v>-4.194217368555022</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-3.814333451406377</v>
       </c>
       <c r="E83">
-        <v>-13.42570482146814</v>
+        <v>-14.87431837178181</v>
       </c>
       <c r="F83">
-        <v>-3.337367329648893</v>
+        <v>-3.286799641544997</v>
       </c>
       <c r="G83">
-        <v>-3.256876125656857</v>
+        <v>-3.590850580749612</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-3.72224481135993</v>
       </c>
       <c r="E84">
-        <v>-15.10820499732997</v>
+        <v>-16.54130852416737</v>
       </c>
       <c r="F84">
-        <v>-3.127526955906528</v>
+        <v>-3.708567874884782</v>
       </c>
       <c r="G84">
-        <v>-2.127907264763518</v>
+        <v>-2.855892918303713</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-3.663972279941253</v>
       </c>
       <c r="E85">
-        <v>-14.79376134765936</v>
+        <v>-16.84547706631457</v>
       </c>
       <c r="F85">
-        <v>-3.667139564335974</v>
+        <v>-3.72336500180099</v>
       </c>
       <c r="G85">
-        <v>-2.480993499254486</v>
+        <v>-3.443455161704641</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-3.647808992015584</v>
       </c>
       <c r="E86">
-        <v>-16.90582351094079</v>
+        <v>-17.85962882033235</v>
       </c>
       <c r="F86">
-        <v>-3.692482636657222</v>
+        <v>-4.075174294504746</v>
       </c>
       <c r="G86">
-        <v>-1.86766196937587</v>
+        <v>-2.441419237878038</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-3.687017454141923</v>
       </c>
       <c r="E87">
-        <v>-17.40663650839707</v>
+        <v>-18.7148356651549</v>
       </c>
       <c r="F87">
-        <v>-3.852456949485862</v>
+        <v>-3.992369860553504</v>
       </c>
       <c r="G87">
-        <v>-1.705127425579812</v>
+        <v>-2.766819380024082</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-3.787155227618074</v>
       </c>
       <c r="E88">
-        <v>-18.39538352323181</v>
+        <v>-19.94079320545944</v>
       </c>
       <c r="F88">
-        <v>-3.79819474276548</v>
+        <v>-4.131331805842732</v>
       </c>
       <c r="G88">
-        <v>-1.935223582741317</v>
+        <v>-2.347677830388036</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-3.959658799699802</v>
       </c>
       <c r="E89">
-        <v>-19.53863301426026</v>
+        <v>-21.14820664470256</v>
       </c>
       <c r="F89">
-        <v>-4.055398679497713</v>
+        <v>-4.358874390982924</v>
       </c>
       <c r="G89">
-        <v>-1.679457455468303</v>
+        <v>-2.632530410769085</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-4.205303786428342</v>
       </c>
       <c r="E90">
-        <v>-21.99621774432693</v>
+        <v>-22.2109806241407</v>
       </c>
       <c r="F90">
-        <v>-4.298937039185962</v>
+        <v>-4.425199283822871</v>
       </c>
       <c r="G90">
-        <v>-1.689888984462547</v>
+        <v>-2.253029333420272</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-4.532761781859121</v>
       </c>
       <c r="E91">
-        <v>-23.57007077179673</v>
+        <v>-24.48315604291132</v>
       </c>
       <c r="F91">
-        <v>-4.277956977975259</v>
+        <v>-4.938941149895485</v>
       </c>
       <c r="G91">
-        <v>-1.822621997314086</v>
+        <v>-2.966518108043998</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-4.937566326357015</v>
       </c>
       <c r="E92">
-        <v>-25.46330801407951</v>
+        <v>-25.56362729877143</v>
       </c>
       <c r="F92">
-        <v>-4.682657529347763</v>
+        <v>-5.124190608918345</v>
       </c>
       <c r="G92">
-        <v>-1.585447893789619</v>
+        <v>-2.491358817337944</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-5.42573060591058</v>
       </c>
       <c r="E93">
-        <v>-27.67209838216477</v>
+        <v>-27.8436822623154</v>
       </c>
       <c r="F93">
-        <v>-4.520252786559309</v>
+        <v>-5.254519309135596</v>
       </c>
       <c r="G93">
-        <v>-2.151693534463181</v>
+        <v>-3.119379237774306</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-5.987161480168684</v>
       </c>
       <c r="E94">
-        <v>-29.07185422640969</v>
+        <v>-29.67708930600884</v>
       </c>
       <c r="F94">
-        <v>-4.243216077469251</v>
+        <v>-5.045455944017057</v>
       </c>
       <c r="G94">
-        <v>-2.617576676568198</v>
+        <v>-3.512579352564624</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-6.619586996140034</v>
       </c>
       <c r="E95">
-        <v>-31.80522302354348</v>
+        <v>-32.07896701307016</v>
       </c>
       <c r="F95">
-        <v>-4.65073224964387</v>
+        <v>-5.484160977274481</v>
       </c>
       <c r="G95">
-        <v>-3.93244922221931</v>
+        <v>-4.605205044527843</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-7.313268832612638</v>
       </c>
       <c r="E96">
-        <v>-32.80987856756717</v>
+        <v>-34.10680408828291</v>
       </c>
       <c r="F96">
-        <v>-4.846691670817524</v>
+        <v>-5.166627870963763</v>
       </c>
       <c r="G96">
-        <v>-3.869211181328152</v>
+        <v>-4.746052204496136</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-8.049205116764627</v>
       </c>
       <c r="E97">
-        <v>-35.91178590063021</v>
+        <v>-36.54476467623735</v>
       </c>
       <c r="F97">
-        <v>-4.780167969800904</v>
+        <v>-5.664988611101196</v>
       </c>
       <c r="G97">
-        <v>-4.342314623254318</v>
+        <v>-3.719892335324864</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-8.828036464735526</v>
       </c>
       <c r="E98">
-        <v>-38.05274425655458</v>
+        <v>-38.59016543788886</v>
       </c>
       <c r="F98">
-        <v>-5.122706174532528</v>
+        <v>-5.781460381404417</v>
       </c>
       <c r="G98">
-        <v>-4.713099034198231</v>
+        <v>-5.681609063348634</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-9.608135994369405</v>
       </c>
       <c r="E99">
-        <v>-40.49219018398352</v>
+        <v>-41.28145339030638</v>
       </c>
       <c r="F99">
-        <v>-4.938854171318192</v>
+        <v>-5.674111421308227</v>
       </c>
       <c r="G99">
-        <v>-5.016335073958854</v>
+        <v>-5.902018564262232</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-10.42055360435553</v>
       </c>
       <c r="E100">
-        <v>-42.42908870841125</v>
+        <v>-43.48685872407091</v>
       </c>
       <c r="F100">
-        <v>-5.008795716238762</v>
+        <v>-5.681991680411059</v>
       </c>
       <c r="G100">
-        <v>-5.781676923364184</v>
+        <v>-6.592959213217982</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-11.18288595031812</v>
       </c>
       <c r="E101">
-        <v>-45.25997592906323</v>
+        <v>-45.31355909775899</v>
       </c>
       <c r="F101">
-        <v>-5.178867827707529</v>
+        <v>-5.897625655768604</v>
       </c>
       <c r="G101">
-        <v>-6.375227943645655</v>
+        <v>-6.897890252294712</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-12.01112664645551</v>
       </c>
       <c r="E102">
-        <v>-47.07539360976119</v>
+        <v>-47.67591681215536</v>
       </c>
       <c r="F102">
-        <v>-5.149019265082454</v>
+        <v>-5.730220058969449</v>
       </c>
       <c r="G102">
-        <v>-7.016371366599688</v>
+        <v>-7.591856739873355</v>
       </c>
     </row>
   </sheetData>
